--- a/artfynd/A 33545-2021 artfynd.xlsx
+++ b/artfynd/A 33545-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33545-2021 artfynd.xlsx
+++ b/artfynd/A 33545-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104023376</v>
+        <v>104023379</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544498.7448646992</v>
+        <v>544418</v>
       </c>
       <c r="R2" t="n">
-        <v>7093603.388855692</v>
+        <v>7093770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104023378</v>
+        <v>104023368</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544434.9801045139</v>
+        <v>544597</v>
       </c>
       <c r="R3" t="n">
-        <v>7093755.826008579</v>
+        <v>7093423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +895,238 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104023376</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544499</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7093604</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104023378</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>544435</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7093756</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
